--- a/data/trans_dic/P32E$eventos_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32E$eventos_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos</t>
+          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,24</t>
+          <t>0,0; 14,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,54</t>
+          <t>0,0; 43,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,15</t>
+          <t>0,0; 13,61</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,16</t>
+          <t>0,0; 40,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,73</t>
+          <t>0,0; 20,64</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 90,66</t>
+          <t>0,0; 81,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,3</t>
+          <t>0,0; 19,02</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,88</t>
+          <t>0,0; 11,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,51</t>
+          <t>0,0; 9,15</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,46</t>
+          <t>0,58; 5,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 21,94</t>
+          <t>2,17; 22,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,78</t>
+          <t>1,63; 8,08</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos</t>
+          <t>Población que realiza el atracón de alcohol, al menos, en conciertos o eventos (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4523</t>
+          <t>0; 4832</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4816</t>
+          <t>0; 4718</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6809</t>
+          <t>0; 6119</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1907</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 8673</t>
+          <t>0; 8792</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 11111</t>
+          <t>0; 11064</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1690</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4311</t>
+          <t>0; 3863</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4966</t>
+          <t>0; 5459</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6958</t>
+          <t>0; 6403</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1452</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 8240</t>
+          <t>0; 6545</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>897; 9310</t>
+          <t>831; 8005</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1634; 12007</t>
+          <t>1189; 12378</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3600; 15474</t>
+          <t>3232; 16067</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$eventos_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32E$eventos_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,15</t>
+          <t>0,0; 13,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,64</t>
+          <t>0,0; 36,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,61</t>
+          <t>0,0; 14,3</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,71</t>
+          <t>0,0; 35,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,64</t>
+          <t>0,0; 14,82</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,25</t>
+          <t>0,0; 75,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,02</t>
+          <t>0,0; 15,73</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,85</t>
+          <t>0,0; 11,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,15</t>
+          <t>0,0; 8,42</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,56</t>
+          <t>0,55; 4,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 22,62</t>
+          <t>2,55; 19,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 8,08</t>
+          <t>1,71; 7,26</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1999</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4832</t>
+          <t>0; 4603</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4718</t>
+          <t>0; 4002</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6119</t>
+          <t>0; 6590</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>3060</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 8792</t>
+          <t>0; 8837</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 11064</t>
+          <t>0; 9493</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1060</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3863</t>
+          <t>0; 4729</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5459</t>
+          <t>0; 5722</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2037</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6403</t>
+          <t>0; 6439</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6545</t>
+          <t>0; 6664</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>8157</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>831; 8005</t>
+          <t>880; 7733</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1189; 12378</t>
+          <t>1638; 12261</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3232; 16067</t>
+          <t>3861; 16381</t>
         </is>
       </c>
     </row>
